--- a/eval/manual_curation/RA2/RA2-M3.xlsx
+++ b/eval/manual_curation/RA2/RA2-M3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luohaomiao/Desktop/code/violin_org/violin_cache_20250321/examples/extension_manually_checking/curation_correction_250529/RA2/0602/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luohaomiao/Desktop/code/violin_org/master/VIOLIN/eval/manual_curation/RA2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78FA115D-1387-F146-8A0F-9E4C8D3BD742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43B93E4-B7BC-444A-9375-18829B923A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31060" yWindow="-240" windowWidth="29400" windowHeight="17780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1980" yWindow="-18580" windowWidth="30240" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RA2-M3_1" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11037" uniqueCount="1169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11065" uniqueCount="1172">
   <si>
     <t>Regulator Name</t>
   </si>
@@ -3546,6 +3546,15 @@
   </si>
   <si>
     <t>mTORC2 can function as the elusive PDK-2 which phosphorylates Akt-1 on S473 in response to growth factor stimulation [ XREF_BIBR ] .</t>
+  </si>
+  <si>
+    <t>p38.p</t>
+  </si>
+  <si>
+    <t>As shown in XREF_FIG , Src over-expression significantly increased phosphorylation of p38 and the Src induced phosphorylation of p38 is completely blocked by PP2 pre-treatment .</t>
+  </si>
+  <si>
+    <t>Inhibition of Src completely blocked EP2 induced p38 phosphorylation and overexpression of Src increased the level of p38 phosphorylation , indicating that Src is upstream kinase for EP2 induced p38 phosphorylation .</t>
   </si>
 </sst>
 </file>
@@ -3581,7 +3590,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3660,6 +3669,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA9694"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -3695,7 +3710,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -3722,11 +3737,33 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -4024,7 +4061,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CBDA7AB-8ED1-9A42-B5B7-0A206E716B44}">
-  <dimension ref="A1:AC656"/>
+  <dimension ref="A1:AC658"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.2">
@@ -38684,8 +38721,112 @@
         <v>38</v>
       </c>
     </row>
+    <row r="657" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A657" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="B657" t="s">
+        <v>29</v>
+      </c>
+      <c r="E657" t="s">
+        <v>30</v>
+      </c>
+      <c r="F657" t="s">
+        <v>1169</v>
+      </c>
+      <c r="I657" t="s">
+        <v>103</v>
+      </c>
+      <c r="J657" t="s">
+        <v>29</v>
+      </c>
+      <c r="M657" t="s">
+        <v>30</v>
+      </c>
+      <c r="N657" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q657" t="s">
+        <v>45</v>
+      </c>
+      <c r="R657" t="s">
+        <v>39</v>
+      </c>
+      <c r="S657" t="s">
+        <v>61</v>
+      </c>
+      <c r="U657" t="s">
+        <v>257</v>
+      </c>
+      <c r="AA657" t="s">
+        <v>1170</v>
+      </c>
+      <c r="AB657" t="s">
+        <v>424</v>
+      </c>
+      <c r="AC657">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="658" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A658" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="B658" t="s">
+        <v>29</v>
+      </c>
+      <c r="E658" t="s">
+        <v>30</v>
+      </c>
+      <c r="F658" t="s">
+        <v>1169</v>
+      </c>
+      <c r="I658" t="s">
+        <v>103</v>
+      </c>
+      <c r="J658" t="s">
+        <v>29</v>
+      </c>
+      <c r="M658" t="s">
+        <v>30</v>
+      </c>
+      <c r="N658" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q658" t="s">
+        <v>45</v>
+      </c>
+      <c r="R658" t="s">
+        <v>39</v>
+      </c>
+      <c r="S658" t="s">
+        <v>61</v>
+      </c>
+      <c r="U658" t="s">
+        <v>257</v>
+      </c>
+      <c r="AA658" t="s">
+        <v>1171</v>
+      </c>
+      <c r="AB658" t="s">
+        <v>424</v>
+      </c>
+      <c r="AC658">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AC694" xr:uid="{3CBDA7AB-8ED1-9A42-B5B7-0A206E716B44}"/>
+  <conditionalFormatting sqref="I657 A657">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>"OR($A=""match"", $B=""match"")"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I658 A658">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>"OR($A=""match"", $B=""match"")"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
